--- a/Raw_Data/Planulae/Larvae_Release/Release_Data.xlsx
+++ b/Raw_Data/Planulae/Larvae_Release/Release_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\Stylophora-pistillata-FPs\Raw_Data\Larvae_Release\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\Stylophora-pistillata-FPs\Raw_Data\Planulae\Larvae_Release\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF2617F-3B5E-4345-B978-F46646013E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE36FED4-72C8-4EE7-A43C-CC467F617A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{04648552-3F89-47B8-B751-87EF3907E17F}"/>
+    <workbookView xWindow="20715" yWindow="7890" windowWidth="24285" windowHeight="12480" activeTab="1" xr2:uid="{04648552-3F89-47B8-B751-87EF3907E17F}"/>
   </bookViews>
   <sheets>
     <sheet name="count" sheetId="2" r:id="rId1"/>
@@ -3643,16 +3643,6 @@
     <row r="58" spans="1:28" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="N57:P57"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="W57:Y57"/>
     <mergeCell ref="T1:V1"/>
@@ -3660,6 +3650,16 @@
     <mergeCell ref="Z1:Z2"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="T57:V57"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3670,7 +3670,10 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3806,7 +3809,7 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <f t="shared" ref="D3:D25" si="0">C7*100/I7</f>
+        <f t="shared" ref="D7" si="0">C7*100/I7</f>
         <v>38.235294117647058</v>
       </c>
       <c r="H7" t="s">
